--- a/data/trans_camb/P2A_ner_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 2,66</t>
+          <t>-3,2; 2,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 7,69</t>
+          <t>0,32; 8,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 3,21</t>
+          <t>-3,7; 3,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 4,18</t>
+          <t>-4,69; 3,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 15,04</t>
+          <t>4,23; 15,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,64; -1,04</t>
+          <t>-7,81; -1,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,68</t>
+          <t>-2,57; 2,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 10,44</t>
+          <t>3,79; 10,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,44</t>
+          <t>-4,37; 0,33</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,4; 132,92</t>
+          <t>-62,83; 137,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 347,65</t>
+          <t>-11,42; 370,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,27; 163,34</t>
+          <t>-66,47; 175,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 95,41</t>
+          <t>-53,22; 87,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,24; 317,28</t>
+          <t>44,02; 331,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,46; -20,22</t>
+          <t>-83,01; -23,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 70,61</t>
+          <t>-40,5; 69,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,28; 282,37</t>
+          <t>56,02; 285,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,81; 18,17</t>
+          <t>-66,75; 13,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 1,75</t>
+          <t>-3,16; 1,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,95</t>
+          <t>-2,68; 1,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,8</t>
+          <t>-3,59; 0,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 3,07</t>
+          <t>-2,65; 3,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 7,84</t>
+          <t>0,95; 7,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,16</t>
+          <t>-2,41; 3,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,81</t>
+          <t>-2,11; 1,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,19</t>
+          <t>-0,18; 4,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,32</t>
+          <t>-2,3; 1,3</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-67,07; 73,19</t>
+          <t>-64,39; 75,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,3; 75,92</t>
+          <t>-54,32; 75,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,59; 35,09</t>
+          <t>-71,58; 38,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 73,14</t>
+          <t>-38,65; 73,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,39; 175,7</t>
+          <t>13,07; 188,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 77,39</t>
+          <t>-32,76; 79,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,9; 49,08</t>
+          <t>-36,77; 51,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 115,55</t>
+          <t>-4,25; 111,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 33,37</t>
+          <t>-39,25; 38,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,08</t>
+          <t>0,58; 4,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,7</t>
+          <t>0,31; 3,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,63</t>
+          <t>1,42; 6,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,89</t>
+          <t>-0,51; 3,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 11,92</t>
+          <t>5,3; 11,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,39</t>
+          <t>2,35; 6,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,98</t>
+          <t>0,42; 2,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,36</t>
+          <t>3,36; 7,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,54</t>
+          <t>2,46; 5,53</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,69; 1109,47</t>
+          <t>-64,57; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>239,11; 3826,29</t>
+          <t>242,66; 3683,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>97,82; 2186,46</t>
+          <t>79,5; 2167,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,17; 1349,59</t>
+          <t>11,02; 1326,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>252,24; 3960,11</t>
+          <t>251,2; 3637,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>188,77; 2967,0</t>
+          <t>168,96; 2902,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,61</t>
+          <t>-1,79; 2,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,54</t>
+          <t>0,3; 5,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 7,76</t>
+          <t>0,86; 7,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,08</t>
+          <t>1,27; 8,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 8,2</t>
+          <t>1,25; 7,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,31</t>
+          <t>-3,36; 2,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,76</t>
+          <t>0,62; 4,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,98</t>
+          <t>1,6; 5,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,89</t>
+          <t>-0,8; 3,48</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,72; 269,35</t>
+          <t>-64,19; 261,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 542,71</t>
+          <t>-9,26; 564,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,89; 689,52</t>
+          <t>12,88; 742,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,94; 294,4</t>
+          <t>21,08; 304,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,39; 313,76</t>
+          <t>15,49; 306,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,99; 83,79</t>
+          <t>-60,9; 88,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,03; 211,28</t>
+          <t>14,66; 225,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>39,2; 265,08</t>
+          <t>37,19; 268,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 171,19</t>
+          <t>-21,96; 142,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,77</t>
+          <t>1,1; 11,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 7,79</t>
+          <t>-0,71; 7,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,56</t>
+          <t>-6,21; -0,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 12,65</t>
+          <t>1,1; 12,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 12,48</t>
+          <t>0,09; 12,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -1,6</t>
+          <t>-9,49; -1,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,28; 10,16</t>
+          <t>2,4; 10,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 8,86</t>
+          <t>1,53; 8,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -1,41</t>
+          <t>-6,47; -1,3</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5,74; 444,76</t>
+          <t>10,38; 513,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,86; 314,64</t>
+          <t>-21,09; 331,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-93,15; 13,18</t>
+          <t>-94,69; 17,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 271,59</t>
+          <t>11,24; 283,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 271,42</t>
+          <t>-1,21; 277,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,32; -32,43</t>
+          <t>-86,62; -26,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,73; 257,91</t>
+          <t>32,2; 261,44</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14,34; 203,53</t>
+          <t>17,42; 211,96</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-83,37; -34,06</t>
+          <t>-83,69; -33,51</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,04</t>
+          <t>-2,93; 0,3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,02</t>
+          <t>0,39; 5,87</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,97</t>
+          <t>0,24; 5,37</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,93</t>
+          <t>-3,32; 2,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,19; 13,05</t>
+          <t>4,25; 12,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,91</t>
+          <t>-2,89; 2,72</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,31</t>
+          <t>-2,41; 1,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,54</t>
+          <t>3,22; 8,7</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,13</t>
+          <t>-0,74; 3,18</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1230,36</t>
+          <t>-2,61; 1110,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 910,39</t>
+          <t>-12,52; 1040,65</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-62,36; 142,79</t>
+          <t>-66,29; 152,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>63,2; 576,55</t>
+          <t>65,56; 584,68</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-54,69; 144,33</t>
+          <t>-53,83; 134,76</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-64,7; 79,54</t>
+          <t>-70,13; 80,02</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>75,85; 521,1</t>
+          <t>85,47; 530,01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 182,19</t>
+          <t>-21,31; 193,06</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,78</t>
+          <t>-0,42; 2,64</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,65</t>
+          <t>0,68; 4,42</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,81</t>
+          <t>1,4; 5,95</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,83</t>
+          <t>-2,99; 0,8</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,7; 10,44</t>
+          <t>4,87; 10,72</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,17; 56,94</t>
+          <t>2,1; 60,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,18</t>
+          <t>-1,31; 1,06</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,77</t>
+          <t>3,49; 6,92</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,46; 47,63</t>
+          <t>2,59; 44,78</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 256,27</t>
+          <t>-20,7; 237,08</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>22,19; 442,92</t>
+          <t>22,65; 395,1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>33,51; 501,08</t>
+          <t>45,63; 496,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-65,96; 41,6</t>
+          <t>-67,0; 34,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>98,82; 446,94</t>
+          <t>101,61; 427,18</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>55,72; 2800,83</t>
+          <t>56,4; 2490,32</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-40,12; 55,73</t>
+          <t>-40,87; 55,59</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>94,13; 326,5</t>
+          <t>110,47; 357,53</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>82,88; 1956,68</t>
+          <t>90,47; 2223,56</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,85</t>
+          <t>-3,31; 0,76</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,72</t>
+          <t>-1,74; 2,53</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,52; -0,9</t>
+          <t>-4,88; -0,84</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,25; -0,04</t>
+          <t>-4,31; -0,11</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,82</t>
+          <t>2,12; 7,54</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,44</t>
+          <t>-3,74; 0,45</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,31; -0,19</t>
+          <t>-3,28; -0,13</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,5</t>
+          <t>0,9; 4,7</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,02; -0,76</t>
+          <t>-3,94; -0,79</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-60,76; 29,6</t>
+          <t>-62,29; 24,59</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-30,38; 86,42</t>
+          <t>-32,07; 81,7</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-85,51; -25,15</t>
+          <t>-84,65; -23,6</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-60,77; -1,27</t>
+          <t>-60,13; -1,68</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>26,16; 166,13</t>
+          <t>28,72; 164,62</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-53,2; 10,32</t>
+          <t>-50,93; 12,06</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-55,6; -2,89</t>
+          <t>-55,32; -2,39</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>13,06; 106,11</t>
+          <t>14,96; 114,18</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-67,01; -19,1</t>
+          <t>-66,97; -18,79</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,11</t>
+          <t>-0,5; 1,14</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,69</t>
+          <t>0,8; 2,6</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,51</t>
+          <t>-0,56; 1,31</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,41</t>
+          <t>-0,68; 1,44</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,8</t>
+          <t>5,09; 7,78</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 22,37</t>
+          <t>-0,33; 21,52</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,97</t>
+          <t>-0,32; 0,97</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,94</t>
+          <t>3,36; 4,89</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 12,78</t>
+          <t>-0,0; 12,06</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 46,48</t>
+          <t>-15,98; 49,47</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>24,92; 113,86</t>
+          <t>22,82; 103,36</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 63,21</t>
+          <t>-17,99; 53,33</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 34,39</t>
+          <t>-12,99; 35,32</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>100,0; 189,91</t>
+          <t>100,08; 191,11</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 516,71</t>
+          <t>-7,25; 471,61</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 27,58</t>
+          <t>-8,14; 28,83</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>79,92; 143,89</t>
+          <t>84,56; 148,08</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 356,2</t>
+          <t>-0,42; 331,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,06</t>
+          <t>-3,92</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>-2,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,56</t>
+          <t>-3,07; 3,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 8,16</t>
+          <t>-0,3; 7,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,56</t>
+          <t>-3,62; 2,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 3,89</t>
+          <t>-4,21; 4,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 15,38</t>
+          <t>4,72; 15,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -1,36</t>
+          <t>-7,52; -0,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 2,54</t>
+          <t>-2,72; 2,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,54</t>
+          <t>3,83; 10,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,33</t>
+          <t>-4,41; 0,06</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>-10,91%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-62,98%</t>
+          <t>-60,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-38,99%</t>
+          <t>-42,64%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 137,31</t>
+          <t>-63,59; 167,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 370,9</t>
+          <t>-14,45; 361,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-66,47; 175,21</t>
+          <t>-66,01; 100,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,22; 87,44</t>
+          <t>-48,93; 96,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,02; 331,08</t>
+          <t>54,28; 356,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,01; -23,3</t>
+          <t>-81,4; -19,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,5; 69,95</t>
+          <t>-43,5; 67,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>56,02; 285,64</t>
+          <t>60,94; 289,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,75; 13,06</t>
+          <t>-67,81; 2,34</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-1,27</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-0,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,74</t>
+          <t>-3,25; 1,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,93</t>
+          <t>-2,96; 1,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,8</t>
+          <t>-3,55; 1,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 3,0</t>
+          <t>-2,78; 3,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 7,72</t>
+          <t>1,12; 8,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 3,25</t>
+          <t>-2,83; 2,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,96</t>
+          <t>-1,97; 1,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,19</t>
+          <t>0,27; 4,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,3</t>
+          <t>-2,19; 1,02</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-34,22%</t>
+          <t>-33,86%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-10,55%</t>
+          <t>-11,14%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-64,39; 75,4</t>
+          <t>-67,01; 67,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,32; 75,95</t>
+          <t>-59,1; 69,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,58; 38,35</t>
+          <t>-71,31; 44,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,65; 73,88</t>
+          <t>-36,62; 77,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,07; 188,72</t>
+          <t>13,37; 192,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,76; 79,97</t>
+          <t>-37,21; 65,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,77; 51,0</t>
+          <t>-37,17; 45,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 111,92</t>
+          <t>3,46; 113,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 38,3</t>
+          <t>-38,15; 30,91</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>3,04</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,31</t>
+          <t>4,28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,81</t>
+          <t>3,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,48</t>
+          <t>0,58; 4,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,5</t>
+          <t>0,31; 3,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,12</t>
+          <t>1,27; 5,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,32</t>
+          <t>-0,55; 2,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 11,71</t>
+          <t>5,14; 11,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,44</t>
+          <t>2,38; 6,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,86</t>
+          <t>0,35; 2,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 7,09</t>
+          <t>3,29; 7,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,53</t>
+          <t>2,36; 5,36</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1068,9%</t>
+          <t>999,25%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>499,39%</t>
+          <t>495,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>645,62%</t>
+          <t>627,42%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,57; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>242,66; 3683,52</t>
+          <t>234,45; 3893,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79,5; 2167,65</t>
+          <t>92,95; 2097,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,02; 1326,87</t>
+          <t>11,56; 1205,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>251,2; 3637,9</t>
+          <t>251,69; 3429,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>168,96; 2902,79</t>
+          <t>159,96; 2781,57</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,61</t>
+          <t>-1,56; 2,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 5,83</t>
+          <t>0,31; 5,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,53</t>
+          <t>0,75; 7,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 8,17</t>
+          <t>1,33; 7,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,94</t>
+          <t>1,15; 7,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,28</t>
+          <t>-2,38; 3,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,67</t>
+          <t>0,58; 4,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,93</t>
+          <t>1,27; 5,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,48</t>
+          <t>-0,19; 4,17</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>196,51%</t>
+          <t>172,18%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-11,88%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,19; 261,96</t>
+          <t>-60,26; 263,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 564,9</t>
+          <t>-4,44; 529,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,88; 742,68</t>
+          <t>11,38; 633,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,08; 304,58</t>
+          <t>16,17; 262,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,49; 306,15</t>
+          <t>20,67; 268,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,9; 88,88</t>
+          <t>-46,37; 116,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,66; 225,2</t>
+          <t>12,93; 215,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>37,19; 268,38</t>
+          <t>33,43; 280,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 142,51</t>
+          <t>-11,79; 188,02</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,85</t>
+          <t>-2,92</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,77</t>
+          <t>-4,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>-3,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,61</t>
+          <t>0,97; 10,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,92</t>
+          <t>-0,69; 7,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,21; -0,26</t>
+          <t>-5,97; -0,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 12,43</t>
+          <t>0,9; 12,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 12,28</t>
+          <t>1,21; 12,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,49; -1,28</t>
+          <t>-8,79; -0,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,39</t>
+          <t>2,52; 10,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,58</t>
+          <t>1,34; 8,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -1,3</t>
+          <t>-6,7; -1,55</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-71,4%</t>
+          <t>-73,03%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-66,8%</t>
+          <t>-59,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-66,53%</t>
+          <t>-63,88%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10,38; 513,23</t>
+          <t>8,88; 497,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 331,03</t>
+          <t>-17,87; 366,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-94,69; 17,67</t>
+          <t>-94,11; 10,64</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,24; 283,19</t>
+          <t>2,17; 268,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 277,8</t>
+          <t>6,91; 273,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-86,62; -26,97</t>
+          <t>-82,21; -12,5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,2; 261,44</t>
+          <t>34,24; 246,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>17,42; 211,96</t>
+          <t>13,16; 207,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-83,69; -33,51</t>
+          <t>-81,76; -34,2</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,24</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,3</t>
+          <t>-2,95; 0,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,39; 5,87</t>
+          <t>0,4; 6,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,24; 5,37</t>
+          <t>-0,01; 4,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 2,91</t>
+          <t>-3,43; 2,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,93</t>
+          <t>4,2; 13,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,72</t>
+          <t>-3,01; 2,62</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,18</t>
+          <t>-2,15; 1,25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,7</t>
+          <t>3,28; 8,66</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,18</t>
+          <t>-0,62; 3,13</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>172,21%</t>
+          <t>159,09%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1110,64</t>
+          <t>-10,06; 1214,34</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 1040,65</t>
+          <t>-10,96; 959,1</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-66,29; 152,85</t>
+          <t>-63,16; 138,32</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>65,56; 584,68</t>
+          <t>57,76; 552,0</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-53,83; 134,76</t>
+          <t>-52,1; 122,45</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-70,13; 80,02</t>
+          <t>-64,78; 86,01</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>85,47; 530,01</t>
+          <t>89,15; 471,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 193,06</t>
+          <t>-17,74; 187,19</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,17</t>
+          <t>3,35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,43</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>16,11</t>
+          <t>3,33</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,64</t>
+          <t>-0,51; 2,53</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,42</t>
+          <t>0,57; 4,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,95</t>
+          <t>1,42; 5,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,8</t>
+          <t>-2,95; 0,75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,87; 10,72</t>
+          <t>4,8; 10,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,1; 60,65</t>
+          <t>1,06; 5,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,06</t>
+          <t>-1,34; 1,07</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,92</t>
+          <t>3,42; 6,97</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,59; 44,78</t>
+          <t>2,01; 4,87</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>179,13%</t>
+          <t>189,15%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>744,59%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>617,7%</t>
+          <t>127,84%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 237,08</t>
+          <t>-24,75; 207,74</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>22,65; 395,1</t>
+          <t>17,6; 352,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>45,63; 496,01</t>
+          <t>53,98; 495,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-67,0; 34,52</t>
+          <t>-68,78; 34,17</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>101,61; 427,18</t>
+          <t>101,73; 413,61</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>56,4; 2490,32</t>
+          <t>18,39; 213,03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-40,87; 55,59</t>
+          <t>-42,02; 51,44</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>110,47; 357,53</t>
+          <t>106,26; 351,5</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>90,47; 2223,56</t>
+          <t>62,12; 238,64</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-1,84</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>-1,59</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,22</t>
+          <t>-1,72</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,76</t>
+          <t>-3,28; 0,85</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,53</t>
+          <t>-1,62; 2,48</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,84</t>
+          <t>-3,97; -0,07</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,31; -0,11</t>
+          <t>-4,31; -0,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,54</t>
+          <t>1,86; 7,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,45</t>
+          <t>-3,89; 0,4</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,28; -0,13</t>
+          <t>-3,21; -0,09</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,7</t>
+          <t>0,9; 4,61</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,79</t>
+          <t>-3,09; -0,28</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-58,81%</t>
+          <t>-42,94%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-27,43%</t>
+          <t>-27,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-44,11%</t>
+          <t>-34,13%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-62,29; 24,59</t>
+          <t>-60,97; 31,3</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 81,7</t>
+          <t>-31,6; 76,11</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-84,65; -23,6</t>
+          <t>-68,63; 2,27</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-60,13; -1,68</t>
+          <t>-61,15; 0,2</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>28,72; 164,62</t>
+          <t>25,45; 176,04</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 12,06</t>
+          <t>-53,38; 11,03</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-55,32; -2,39</t>
+          <t>-54,72; -1,23</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>14,96; 114,18</t>
+          <t>14,38; 106,28</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-66,97; -18,79</t>
+          <t>-51,69; -5,81</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>0,46</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,14</t>
+          <t>-0,53; 1,13</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,6</t>
+          <t>0,8; 2,68</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,31</t>
+          <t>-0,14; 1,6</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,44</t>
+          <t>-0,71; 1,4</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,78</t>
+          <t>5,19; 7,78</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 21,52</t>
+          <t>-0,79; 1,13</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,97</t>
+          <t>-0,32; 0,98</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,89</t>
+          <t>3,38; 5,0</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 12,06</t>
+          <t>-0,13; 1,11</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>113,66%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 49,47</t>
+          <t>-17,06; 48,67</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>22,82; 103,36</t>
+          <t>23,91; 110,49</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 53,33</t>
+          <t>-4,84; 65,66</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 35,32</t>
+          <t>-14,37; 33,57</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>100,08; 191,11</t>
+          <t>101,58; 191,26</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 471,61</t>
+          <t>-14,81; 27,78</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 28,83</t>
+          <t>-8,16; 29,03</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>84,56; 148,08</t>
+          <t>84,69; 146,99</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 331,04</t>
+          <t>-3,83; 33,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
